--- a/data/trans_dic/P5_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con algún problema medioambiental importante en la zona de residencia</t>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,46; 38,06</t>
+          <t>21,79; 38,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,87; 45,7</t>
+          <t>30,31; 46,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,06; 39,55</t>
+          <t>24,57; 39,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,78; 31,9</t>
+          <t>14,69; 31,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,55; 43,04</t>
+          <t>26,98; 43,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,07; 47,7</t>
+          <t>32,55; 47,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,94; 41,23</t>
+          <t>25,96; 41,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,36; 20,92</t>
+          <t>8,1; 21,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,67; 38,24</t>
+          <t>26,89; 38,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34,21; 45,14</t>
+          <t>33,67; 44,41</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,53; 37,97</t>
+          <t>27,25; 38,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,66; 23,72</t>
+          <t>12,91; 22,98</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,27; 33,05</t>
+          <t>22,16; 32,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,32; 40,74</t>
+          <t>28,15; 40,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,09; 40,99</t>
+          <t>28,41; 40,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 29,55</t>
+          <t>17,61; 28,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 27,49</t>
+          <t>17,53; 27,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,39; 44,85</t>
+          <t>32,85; 44,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,62; 41,16</t>
+          <t>30,32; 40,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,53; 28,23</t>
+          <t>17,27; 27,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,54; 28,25</t>
+          <t>20,93; 28,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,6; 41,56</t>
+          <t>32,75; 41,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,51; 39,41</t>
+          <t>31,43; 39,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,71; 26,65</t>
+          <t>18,97; 26,57</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,16; 37,64</t>
+          <t>22,02; 37,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,17; 45,66</t>
+          <t>30,03; 46,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,62; 43,37</t>
+          <t>30,0; 43,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 23,19</t>
+          <t>13,07; 23,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,41; 38,97</t>
+          <t>23,99; 38,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,93; 41,55</t>
+          <t>27,08; 41,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,45; 46,69</t>
+          <t>33,19; 46,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,93; 23,97</t>
+          <t>13,85; 23,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,27; 35,82</t>
+          <t>25,17; 36,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,5; 41,47</t>
+          <t>29,98; 41,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,55; 42,97</t>
+          <t>33,3; 42,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,52; 22,27</t>
+          <t>14,85; 22,38</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,62; 33,69</t>
+          <t>22,02; 34,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,23; 52,18</t>
+          <t>36,78; 52,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,1; 43,07</t>
+          <t>27,66; 42,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,72; 46,61</t>
+          <t>12,47; 45,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,33; 35,2</t>
+          <t>22,89; 35,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,75; 46,07</t>
+          <t>32,0; 46,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,44; 48,09</t>
+          <t>34,22; 48,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 18,18</t>
+          <t>10,42; 18,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,23; 32,68</t>
+          <t>24,12; 32,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,51; 47,01</t>
+          <t>36,4; 46,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,09; 43,81</t>
+          <t>33,0; 43,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,97; 35,29</t>
+          <t>12,92; 30,63</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,11; 31,24</t>
+          <t>25,01; 31,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,46; 41,73</t>
+          <t>34,63; 41,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,61; 38,46</t>
+          <t>31,7; 38,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,9; 31,97</t>
+          <t>17,06; 30,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,8; 31,05</t>
+          <t>24,75; 30,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,92; 41,77</t>
+          <t>34,62; 41,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,31; 40,94</t>
+          <t>33,9; 40,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,85</t>
+          <t>14,7; 19,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,76; 30,3</t>
+          <t>25,67; 30,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,81; 40,49</t>
+          <t>35,66; 40,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,97; 38,42</t>
+          <t>33,78; 38,66</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,67; 25,18</t>
+          <t>16,79; 24,46</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con algún problema medioambiental importante en la zona de residencia (tasa de respuesta: 99,95%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>22983</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39185</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32916</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12728</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>30687</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>44905</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>32778</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>8384</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>53670</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>84089</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>65695</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>21112</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>17117; 29877</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>31562; 48097</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25238; 40314</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8447; 18096</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>23866; 38557</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>36471; 53219</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>25508; 40897</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>4974; 13423</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>44915; 64805</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>72782; 96008</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>54758; 76510</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>15359; 27333</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>51203</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54313</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54278</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35793</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>41681</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75605</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>75308</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>40553</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>92884</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>129918</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>129586</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>76346</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>41496; 61294</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>44854; 64370</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>44402; 63883</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>27803; 45362</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>33085; 51186</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>63470; 86779</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>63860; 85604</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>31522; 50352</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>78689; 106704</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>115480; 146356</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>115292; 145266</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>64578; 90439</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>25209</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>36546</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53393</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31223</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>32333</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>34331</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>52381</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>38837</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>57542</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>70877</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>105774</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>70059</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>19042; 32186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>29421; 45145</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43292; 63143</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22730; 40860</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>24769; 40206</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>27574; 42506</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>43867; 61602</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>29299; 50568</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>47758; 68616</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>59902; 82617</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>92070; 117892</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>57250; 86269</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>42060</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51365</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42875</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>61326</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42946</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>51301</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>52926</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>42445</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>85007</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>102665</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>95801</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>103770</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>33266; 51412</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>42492; 60594</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>33449; 51400</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>34339; 126399</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>33902; 52391</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>42143; 60616</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>44486; 62795</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31832; 56110</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>72166; 97625</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>90000; 116044</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>82815; 108909</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>75055; 177920</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>141455</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>181408</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>183462</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>141069</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>130218</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>289103</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>387550</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>396856</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>271288</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>125887; 158034</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>165150; 199619</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>166203; 201377</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>113404; 205224</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>130804; 162956</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>186550; 224109</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>193596; 231374</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>111905; 149274</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>264926; 311705</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>362249; 412672</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>369934; 423452</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>239320; 348796</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,79; 38,03</t>
+          <t>21,63; 38,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,31; 46,19</t>
+          <t>29,37; 44,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,57; 39,25</t>
+          <t>25,31; 39,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,69; 31,46</t>
+          <t>15,24; 31,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,98; 43,58</t>
+          <t>26,91; 42,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,55; 47,5</t>
+          <t>32,89; 48,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,96; 41,62</t>
+          <t>25,9; 42,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 21,85</t>
+          <t>8,15; 21,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,89; 38,8</t>
+          <t>26,44; 38,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,67; 44,41</t>
+          <t>33,11; 44,37</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,25; 38,07</t>
+          <t>27,52; 37,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 22,98</t>
+          <t>12,55; 24,05</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,16; 32,73</t>
+          <t>22,63; 32,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,15; 40,4</t>
+          <t>27,71; 40,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,41; 40,88</t>
+          <t>29,64; 41,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,61; 28,73</t>
+          <t>17,49; 28,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,53; 27,12</t>
+          <t>17,48; 26,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,85; 44,91</t>
+          <t>33,39; 44,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,32; 40,65</t>
+          <t>30,2; 41,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,27; 27,58</t>
+          <t>17,6; 28,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20,93; 28,38</t>
+          <t>21,32; 28,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,75; 41,51</t>
+          <t>33,02; 41,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,43; 39,6</t>
+          <t>31,21; 39,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 26,57</t>
+          <t>18,52; 26,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,02; 37,22</t>
+          <t>21,33; 37,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30,03; 46,08</t>
+          <t>29,9; 45,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,0; 43,75</t>
+          <t>31,09; 43,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,07; 23,5</t>
+          <t>13,31; 23,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,99; 38,94</t>
+          <t>24,31; 39,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,08; 41,75</t>
+          <t>26,4; 42,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,19; 46,61</t>
+          <t>33,14; 46,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,85; 23,9</t>
+          <t>14,08; 23,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,17; 36,16</t>
+          <t>25,09; 36,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29,98; 41,35</t>
+          <t>30,23; 41,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,3; 42,64</t>
+          <t>33,52; 43,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 22,38</t>
+          <t>14,73; 21,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,02; 34,03</t>
+          <t>21,87; 34,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,78; 52,45</t>
+          <t>36,82; 52,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,66; 42,5</t>
+          <t>28,74; 43,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,47; 45,89</t>
+          <t>12,7; 45,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,89; 35,38</t>
+          <t>23,6; 35,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,0; 46,03</t>
+          <t>32,18; 46,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,22; 48,3</t>
+          <t>33,66; 48,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 18,37</t>
+          <t>10,11; 17,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,12; 32,63</t>
+          <t>24,63; 32,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,4; 46,94</t>
+          <t>36,74; 46,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,0; 43,4</t>
+          <t>32,69; 43,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,92; 30,63</t>
+          <t>12,76; 30,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,01; 31,4</t>
+          <t>24,72; 31,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,63; 41,85</t>
+          <t>34,52; 41,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,7; 38,41</t>
+          <t>31,79; 38,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,06; 30,87</t>
+          <t>16,81; 32,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,75; 30,83</t>
+          <t>25,14; 31,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,62; 41,6</t>
+          <t>35,17; 41,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,9; 40,52</t>
+          <t>34,37; 40,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,7; 19,61</t>
+          <t>14,54; 19,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,67; 30,21</t>
+          <t>25,75; 30,35</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,66; 40,63</t>
+          <t>35,53; 40,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,78; 38,66</t>
+          <t>33,94; 38,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,79; 24,46</t>
+          <t>16,66; 24,06</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17117; 29877</t>
+          <t>16989; 30030</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31562; 48097</t>
+          <t>30579; 46783</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25238; 40314</t>
+          <t>25990; 40370</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8447; 18096</t>
+          <t>8766; 17937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23866; 38557</t>
+          <t>23805; 38033</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36471; 53219</t>
+          <t>36853; 54349</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25508; 40897</t>
+          <t>25455; 41430</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4974; 13423</t>
+          <t>5005; 13359</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44915; 64805</t>
+          <t>44155; 63618</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>72782; 96008</t>
+          <t>71572; 95901</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54758; 76510</t>
+          <t>55305; 75928</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15359; 27333</t>
+          <t>14932; 28606</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41496; 61294</t>
+          <t>42368; 61406</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44854; 64370</t>
+          <t>44150; 64397</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44402; 63883</t>
+          <t>46317; 65286</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27803; 45362</t>
+          <t>27621; 45188</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33085; 51186</t>
+          <t>32992; 50410</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63470; 86779</t>
+          <t>64513; 86521</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63860; 85604</t>
+          <t>63591; 86525</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31522; 50352</t>
+          <t>32124; 51185</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78689; 106704</t>
+          <t>80170; 105774</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115480; 146356</t>
+          <t>116428; 146322</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>115292; 145266</t>
+          <t>114478; 143508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64578; 90439</t>
+          <t>63032; 90202</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19042; 32186</t>
+          <t>18447; 32164</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29421; 45145</t>
+          <t>29296; 44786</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43292; 63143</t>
+          <t>44866; 63391</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22730; 40860</t>
+          <t>23150; 40153</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24769; 40206</t>
+          <t>25100; 40335</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27574; 42506</t>
+          <t>26875; 42821</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43867; 61602</t>
+          <t>43806; 62111</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29299; 50568</t>
+          <t>29795; 50560</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47758; 68616</t>
+          <t>47613; 69293</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59902; 82617</t>
+          <t>60389; 82390</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92070; 117892</t>
+          <t>92677; 120445</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>57250; 86269</t>
+          <t>56789; 84183</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33266; 51412</t>
+          <t>33033; 51582</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42492; 60594</t>
+          <t>42530; 60406</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33449; 51400</t>
+          <t>34762; 52986</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34339; 126399</t>
+          <t>34976; 125659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33902; 52391</t>
+          <t>34952; 52046</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42143; 60616</t>
+          <t>42383; 60656</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44486; 62795</t>
+          <t>43755; 62552</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31832; 56110</t>
+          <t>30893; 54445</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>72166; 97625</t>
+          <t>73675; 98563</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90000; 116044</t>
+          <t>90836; 115709</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82815; 108909</t>
+          <t>82025; 109646</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>75055; 177920</t>
+          <t>74142; 179856</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>125887; 158034</t>
+          <t>124435; 156383</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>165150; 199619</t>
+          <t>164635; 199800</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166203; 201377</t>
+          <t>166664; 201612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>113404; 205224</t>
+          <t>111726; 213673</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>130804; 162956</t>
+          <t>132896; 166042</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>186550; 224109</t>
+          <t>189494; 224900</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>193596; 231374</t>
+          <t>196243; 232148</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>111905; 149274</t>
+          <t>110621; 151459</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>264926; 311705</t>
+          <t>265693; 313158</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>362249; 412672</t>
+          <t>360875; 412380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>369934; 423452</t>
+          <t>371768; 424218</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>239320; 348796</t>
+          <t>237586; 342996</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P5_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34,69%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40,08%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33,36%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16,44%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>29,26%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>37,63%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>32,05%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>33,36%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>19,83%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,63; 38,23</t>
+          <t>26,55; 43,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,37; 44,93</t>
+          <t>32,07; 47,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,31; 39,31</t>
+          <t>24,94; 41,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 31,19</t>
+          <t>10,3; 24,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,91; 42,99</t>
+          <t>22,46; 38,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,89; 48,51</t>
+          <t>30,87; 45,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,9; 42,16</t>
+          <t>25,06; 39,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,15; 21,74</t>
+          <t>15,56; 33,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,44; 38,09</t>
+          <t>26,67; 38,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,11; 44,37</t>
+          <t>34,21; 45,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27,52; 37,78</t>
+          <t>27,53; 37,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,55; 24,05</t>
+          <t>14,16; 26,19</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,08%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>35,76%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>27,35%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>34,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>34,73%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,08%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>39,13%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,76%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,63; 32,79</t>
+          <t>17,36; 27,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,71; 40,41</t>
+          <t>33,39; 44,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,64; 41,78</t>
+          <t>30,62; 41,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,49; 28,62</t>
+          <t>17,44; 28,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,48; 26,71</t>
+          <t>22,27; 33,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,39; 44,78</t>
+          <t>28,32; 40,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,2; 41,09</t>
+          <t>29,09; 40,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,6; 28,04</t>
+          <t>17,47; 28,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,32; 28,13</t>
+          <t>20,54; 28,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33,02; 41,5</t>
+          <t>32,6; 41,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,21; 39,12</t>
+          <t>31,51; 39,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,52; 26,5</t>
+          <t>18,76; 26,54</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31,31%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33,72%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39,63%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18,47%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>29,15%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>37,3%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>37,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>39,63%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>30,33%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>35,48%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>18,36%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30,33%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>35,48%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,33; 37,19</t>
+          <t>24,41; 38,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,9; 45,71</t>
+          <t>25,93; 41,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,09; 43,93</t>
+          <t>32,45; 46,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,31; 23,09</t>
+          <t>14,15; 24,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,31; 39,06</t>
+          <t>21,16; 37,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,4; 42,06</t>
+          <t>29,17; 45,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,14; 46,99</t>
+          <t>30,62; 43,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,08; 23,9</t>
+          <t>13,59; 23,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,09; 36,52</t>
+          <t>25,27; 35,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,23; 41,24</t>
+          <t>30,5; 41,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,52; 43,56</t>
+          <t>33,55; 42,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,73; 21,84</t>
+          <t>14,75; 22,38</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>38,95%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40,71%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14,02%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>27,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>44,46%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>29,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,95%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,87; 34,14</t>
+          <t>23,33; 35,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,82; 52,29</t>
+          <t>32,75; 46,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,74; 43,81</t>
+          <t>33,44; 48,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,7; 45,62</t>
+          <t>10,46; 18,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,6; 35,14</t>
+          <t>21,62; 33,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,18; 46,06</t>
+          <t>36,23; 52,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,66; 48,12</t>
+          <t>28,1; 43,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 17,82</t>
+          <t>11,6; 20,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,63; 32,95</t>
+          <t>24,23; 32,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,74; 46,8</t>
+          <t>36,51; 47,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32,69; 43,69</t>
+          <t>33,09; 43,81</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,76; 30,96</t>
+          <t>11,91; 17,67</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>38,26%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>28,1%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>35,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21,22%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,72; 31,07</t>
+          <t>24,8; 31,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,52; 41,89</t>
+          <t>34,92; 41,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31,79; 38,46</t>
+          <t>34,31; 40,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,81; 32,14</t>
+          <t>15,07; 20,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,14; 31,41</t>
+          <t>25,11; 31,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,17; 41,74</t>
+          <t>34,46; 41,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,37; 40,65</t>
+          <t>31,61; 38,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,54; 19,9</t>
+          <t>16,01; 21,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>25,75; 30,35</t>
+          <t>25,76; 30,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,53; 40,6</t>
+          <t>35,81; 40,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,94; 38,73</t>
+          <t>33,97; 38,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,66; 24,06</t>
+          <t>16,11; 19,86</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>53</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30687</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44905</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32778</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>22983</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>39185</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>32916</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12728</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>30687</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44905</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>32778</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21112</t>
+          <t>20352</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16989; 30030</t>
+          <t>23490; 38079</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30579; 46783</t>
+          <t>35932; 53440</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25990; 40370</t>
+          <t>24507; 40516</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8766; 17937</t>
+          <t>5206; 12560</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23805; 38033</t>
+          <t>17641; 29903</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36853; 54349</t>
+          <t>32144; 47580</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25455; 41430</t>
+          <t>25737; 40619</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5005; 13359</t>
+          <t>8107; 17338</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44155; 63618</t>
+          <t>44550; 63869</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>71572; 95901</t>
+          <t>73949; 97575</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55305; 75928</t>
+          <t>55336; 76303</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14932; 28606</t>
+          <t>14534; 26876</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>55</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>41681</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75605</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75308</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35430</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>51203</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>54313</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>54278</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35793</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>41681</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75605</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75308</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40553</t>
+          <t>32323</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76346</t>
+          <t>67753</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>42368; 61406</t>
+          <t>32770; 51887</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44150; 64397</t>
+          <t>64515; 86655</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46317; 65286</t>
+          <t>64492; 86672</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27621; 45188</t>
+          <t>27467; 44992</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32992; 50410</t>
+          <t>41706; 61890</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64513; 86521</t>
+          <t>45129; 64912</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63591; 86525</t>
+          <t>45457; 64056</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32124; 51185</t>
+          <t>25333; 41310</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80170; 105774</t>
+          <t>77237; 106209</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116428; 146322</t>
+          <t>114937; 146510</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>114478; 143508</t>
+          <t>115600; 144579</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>63032; 90202</t>
+          <t>56742; 80285</t>
         </is>
       </c>
     </row>
@@ -1925,37 +1925,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32333</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>34331</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52381</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36788</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>25209</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>36546</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>53393</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>31223</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>32333</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34331</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>52381</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>32003</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>70059</t>
+          <t>68791</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18447; 32164</t>
+          <t>25207; 40239</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29296; 44786</t>
+          <t>26403; 42307</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44866; 63391</t>
+          <t>42894; 61717</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23150; 40153</t>
+          <t>28172; 47870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25100; 40335</t>
+          <t>18298; 32550</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26875; 42821</t>
+          <t>28582; 44738</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43806; 62111</t>
+          <t>44196; 62590</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29795; 50560</t>
+          <t>23850; 41001</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47613; 69293</t>
+          <t>47948; 67957</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60389; 82390</t>
+          <t>60947; 82850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>92677; 120445</t>
+          <t>92750; 118800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>56789; 84183</t>
+          <t>55264; 83856</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>59</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>42946</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51301</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>52926</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41019</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>42060</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>51365</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>42875</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>61326</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>42946</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51301</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52926</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42445</t>
+          <t>39260</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>103770</t>
+          <t>80279</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>33033; 51582</t>
+          <t>34552; 52126</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42530; 60406</t>
+          <t>43127; 60670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34762; 52986</t>
+          <t>43467; 62523</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34976; 125659</t>
+          <t>30610; 53371</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34952; 52046</t>
+          <t>32667; 50897</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42383; 60656</t>
+          <t>41856; 60283</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43755; 62552</t>
+          <t>33986; 52087</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30893; 54445</t>
+          <t>29758; 52184</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73675; 98563</t>
+          <t>72484; 97779</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>90836; 115709</t>
+          <t>90255; 116215</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>82025; 109646</t>
+          <t>83045; 109929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>74142; 179856</t>
+          <t>65416; 97021</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>168</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>147647</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>206142</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>213394</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>121544</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>141455</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>181408</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>183462</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>141069</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>147647</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>206142</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>213394</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>130218</t>
+          <t>115631</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>271288</t>
+          <t>237175</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>124435; 156383</t>
+          <t>131055; 164091</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>164635; 199800</t>
+          <t>188165; 225055</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166664; 201612</t>
+          <t>195913; 233758</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111726; 213673</t>
+          <t>105481; 140487</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>132896; 166042</t>
+          <t>126371; 157231</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>189494; 224900</t>
+          <t>164366; 199035</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>196243; 232148</t>
+          <t>165689; 201641</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>110621; 151459</t>
+          <t>100715; 134229</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>265693; 313158</t>
+          <t>265826; 312670</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>360875; 412380</t>
+          <t>363763; 411236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>371768; 424218</t>
+          <t>372034; 420792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>237586; 342996</t>
+          <t>214098; 263885</t>
         </is>
       </c>
     </row>
